--- a/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Mensa e buoni pasto per dipendenti.xlsx
+++ b/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Mensa e buoni pasto per dipendenti.xlsx
@@ -152,7 +152,7 @@
     <t>Utilizza il testo indicato per il pulsante. Inserisci il link alla pagina web che rimanda al servizio.</t>
   </si>
   <si>
-    <t>Vedi le convenzioni attive</t>
+    <t>Consulta le convenzioni</t>
   </si>
   <si>
     <t>Link a termini e condizioni d'uso</t>
@@ -468,15 +468,6 @@
       </rPr>
       <t>[Inserire qui indicazioni sulla registrazione e su eventuale app mobile, da compilare a cura e reponsabilità dell'ente]</t>
     </r>
-    <r>
-      <rPr>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t xml:space="preserve">
-Per registrarti, [visita questo sito](URL).</t>
-    </r>
   </si>
   <si>
     <r>
@@ -514,7 +505,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t>[Solo per messaggi premium con allegato]</t>
+      <t>[Solo per messaggi con allegato]</t>
     </r>
     <r>
       <rPr>
@@ -560,7 +551,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t>[Solo per messaggi premium con allegato]</t>
+      <t>[Solo per messaggi con allegato]</t>
     </r>
     <r>
       <rPr>
@@ -617,6 +608,9 @@
     <t>-</t>
   </si>
   <si>
+    <t>Accedi al portale</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -634,7 +628,7 @@
       <rPr>
         <b/>
       </rPr>
-      <t>Allegato (Premium)</t>
+      <t>Allegato</t>
     </r>
     <r>
       <rPr/>
@@ -696,10 +690,6 @@
       </rPr>
       <t>Note aggiuntive</t>
     </r>
-  </si>
-  <si>
-    <t xml:space="preserve">✨ Allegati Premium — Tramite questa funzionalità Premium, disponibile a seconda della tipologia di contratto sottoscritto dall’ente, puoi allegare documenti all'interno del messaggio.
-Questo messaggio è da utilizzare sia per messaggi Premium, sia per messaggi standard. In caso di messaggio standard, ricorda di eliminare ogni riferimento agli allegati dal corpo del messaggio.</t>
   </si>
 </sst>
 </file>
@@ -1376,7 +1366,7 @@
         <v>76</v>
       </c>
       <c r="C6" s="34" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D6" s="34" t="s">
         <v>76</v>
@@ -1390,7 +1380,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="32" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B7" s="34" t="s">
         <v>55</v>
@@ -1410,7 +1400,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="32" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B8" s="34" t="s">
         <v>76</v>
@@ -1419,10 +1409,10 @@
         <v>76</v>
       </c>
       <c r="D8" s="34" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E8" s="34" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F8" s="34" t="s">
         <v>76</v>
@@ -1430,47 +1420,47 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="32" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B9" s="34" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C9" s="34" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D9" s="34" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F9" s="34" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="32" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B10" s="34" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C10" s="34" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D10" s="34" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E10" s="34" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F10" s="34" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="32" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B11" s="34" t="s">
         <v>55</v>
@@ -1479,10 +1469,10 @@
         <v>55</v>
       </c>
       <c r="D11" s="34" t="s">
-        <v>89</v>
+        <v>55</v>
       </c>
       <c r="E11" s="34" t="s">
-        <v>89</v>
+        <v>55</v>
       </c>
       <c r="F11" s="34" t="s">
         <v>55</v>
